--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -647,7 +647,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bước hợp các candidate chưa phải là fusion và không được làm mất tín hiệu của từng đường xử lý.</t>
+          <t>Khi hợp nhất các ứng viên từ hai đường xử lý dense và sparse trước bước reranking, danh sách ứng viên phải giữ đầy đủ: (a) ID ổn định của bản ghi để tránh trùng lặp; (b) Thứ hạng và điểm dense; (c) Thứ hạng và điểm sparse; (d) Dấu vết nguồn (lineage) của từng đường xử lý. Không được giữ hai bản ghi trùng ID hay chỉ giữ điểm số lớn hơn.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp dụng công thức có trọng số và chú ý hệ số `(1 - alpha)` của sparse.</t>
+          <t>Điểm kết hợp: `alpha × dense + (1 - alpha) × sparse` với alpha = 0,6. Với A (dense=0,9, sparse=0,2): điểm = 0,6×0,9 + 0,4×0,2 = 0,54 + 0,08 = 0,62 (mệnh đề a đúng). Với B (dense=0,5, sparse=0,8): điểm = 0,6×0,5 + 0,4×0,8 = 0,30 + 0,32 = 0,62 (mệnh đề b đúng). Hai kết quả có điểm bằng nhau nên hòa và cần dùng quy tắc phá hòa đã khai báo (mệnh đề d đúng). Alpha = 0,6 biểu thị dense đóng góp 60% và sparse đóng góp 40% (mệnh đề e đúng). Mệnh đề c sai vì hai ứng viên có cùng điểm tổng.</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt Weighted formula và Một-trừ-alpha.</t>
+          <t>Với công thức `alpha × dense + (1 - alpha) × sparse` trên candidate có dense=0,2 và sparse=0,9: (a) Khi alpha = 0, điểm = 0 + 1×0,9 = 0,9 và chỉ có tín hiệu sparse được dùng; (b) Khi alpha = 1, điểm = 1×0,2 + 0 = 0,2 và chỉ có tín hiệu dense được dùng; (d) Việc kiểm tra hai điểm biên giá trị (boundary testing) là bước xác minh tính đúng đắn kỹ thuật, tách biệt với việc điều chỉnh tham số alpha tối ưu trên benchmark thực nghiệm.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Fallback phải có điều kiện vào và điều kiện dừng.</t>
+          <t>Trình tự luồng xử lý dự phòng (fallback workflow) có điều kiện vào và điểm dừng rõ ràng: 1. Chạy đường xử lý chính (dense retrieval) (o2) -&gt; 2. Kiểm tra điều kiện kích hoạt có thể quan sát (ví dụ điểm số dưới ngưỡng chất lượng) (o4) -&gt; 3. Chạy đường xử lý dự phòng (BM25) (o5) -&gt; 4. Ghi nhận và giữ nguyên dấu vết nguồn của đường xử lý/kết quả (o3) -&gt; 5. Kết thúc bằng thông báo không có bằng chứng nếu đường dự phòng cũng thất bại (o1).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -678,10 +678,34 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt Các path chạy song song và Định danh bản ghi dùng chung.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt Các path chạy song song và Định danh bản ghi dùng chung.</t>
+- [Đặc tả bản ghi A có 2 nguồn] (1.5 điểm): Mô tả đúng bản ghi A mang cả dense_score, sparse_score và danh sách nguồn ['dense', 'sparse'].
+- [Đặc tả bản ghi B và C nguồn đơn lẻ] (1.5 điểm): Mô tả đúng B chỉ có nguồn sparse (dense null) và C chỉ có nguồn dense (sparse null).
+- [Dấu vết nguồn và thứ hạng minh bạch] (1.0 điểm): Nhấn mạnh tầm quan trọng của provenance tracking để phục vụ tính điểm dung hợp và kiểm toán.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mô tả Bản ghi Hợp nhất trước bước Fusion (Pre-fusion Unified Records for A, B, C):
+Dữ liệu trả về từ hai luồng xử lý song song: Dense trả về `{A: score_dense_A, C: score_dense_C}`; Sparse trả về `{B: score_sparse_B, A: score_sparse_A}`.
+Trước khi tính điểm gộp (RRF hoặc Weighted Score), hệ thống phải hợp nhất thành cấu trúc dữ liệu bản ghi thống nhất lưu vết nguồn gốc đa kênh:
+- **Bản ghi A** (Xuất hiện ở cả hai luồng):
+  + `record_id`: `"A"`
+  + `dense_score`: `score_dense_A`, `dense_rank`: 1 (hoặc thứ hạng tương ứng)
+  + `sparse_score`: `score_sparse_A`, `sparse_rank`: 2
+  + `retrieval_sources`: `["dense", "sparse"]` (được bảo chứng bởi cả hai kênh)
+- **Bản ghi B** (Chỉ xuất hiện ở luồng Sparse):
+  + `record_id`: `"B"`
+  + `dense_score`: `None` (hoặc `0.0`), `dense_rank`: `Infinity`
+  + `sparse_score`: `score_sparse_B`, `sparse_rank`: 1
+  + `retrieval_sources`: `["sparse"]`
+- **Bản ghi C** (Chỉ xuất hiện ở luồng Dense):
+  + `record_id`: `"C"`
+  + `dense_score`: `score_dense_C`, `dense_rank`: 2
+  + `sparse_score`: `None` (hoặc `0.0`), `sparse_rank`: `Infinity`
+  + `retrieval_sources`: `["dense"]`
+2. Ý nghĩa của việc lưu vết nguồn (Provenance Tracking):
+Lưu giữ dấu vết nguồn giúp bộ gộp xếp hạng (Fusion Engine) phân biệt rõ ràng giữa các tài liệu có độ đồng thuận cao giữa hai phương pháp (như A) với các tài liệu chỉ đơn độc xuất hiện ở một phía, đồng thời hỗ trợ kiểm toán và giải thích kết quả cho người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong Hybrid Retrieval chạy song song, bước chuẩn bị dữ liệu trước khi dung hợp (Pre-fusion Aggregation) phải thực hiện Full Outer Join dựa trên `record_id`. Việc ghi nhận chi tiết thứ hạng và điểm số của từng luồng kèm mảng `retrieval_sources` là điều kiện tiên quyết để thuật toán RRF hoặc Weighted Fusion hoạt động chính xác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Documentation: 'Reciprocal Rank Fusion Implementation' &amp; Cormack et al. (2009)</t>
         </is>
       </c>
     </row>
@@ -760,10 +784,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra thang đo của các tín hiệu rồi xác định rõ phương pháp chuẩn hóa.
-Phân tích theo nguyên lý thiết kế: Kiểm tra thang đo của các tín hiệu rồi xác định rõ phương pháp chuẩn hóa.</t>
+- [Xác định nguyên nhân chia cho 0] (1.0 điểm): Chỉ ra mẫu số max - min = 0 do mọi điểm bằng 0.5.
+- [Hành vi chuẩn hóa tất định] (1.5 điểm): Đưa ra xử lý chuẩn: gán điểm chuẩn hóa về 0.0 để vô hiệu hóa tín hiệu không phân biệt và để sparse quyết định thứ hạng.
+- [Các điều tuyệt đối không được làm] (1.5 điểm): Cấm để sập hệ thống (500 error), cấm thêm nhiễu ngẫu nhiên làm đảo lộn thứ tự, cấm bỏ kết quả.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hành vi xác định cho trường hợp mọi điểm bằng nhau (Zero-Variance / Degenerate Case Handling):
+Khi toàn bộ điểm số của Dense Search đều bằng 0,5 (`min_score == max_score == 0.5`), công thức chuẩn hóa Min-Max: `(s - min) / (max - min)` sẽ có mẫu số bằng 0 (Division by Zero).
+- **Hành vi chuẩn hóa đúng (Deterministic Fallback)**: Hệ thống phải xử lý ngoại lệ này một cách tất định: gán toàn bộ điểm số chuẩn hóa của kênh Dense về giá trị trung tính mặc định (Neutral Default Value), cụ thể là `0.0` (hoặc `1.0` tùy quy ước hệ thống, trong đó gán `0.0` là chuẩn nhất để phản ánh rằng kênh này không cung cấp bất kỳ tín hiệu phân biệt nào giữa các tài liệu).
+- Kết quả: Tín hiệu Dense không tạo ra sự chênh lệch thứ hạng; thứ tự sắp xếp và điểm số dung hợp hoàn toàn được quyết định bởi các điểm số khác nhau của kênh Sparse (BM25).
+2. Điều TUYỆT ĐỐI KHÔNG ĐƯỢC LÀM (Strict Prohibitions):
+- Tuyệt đối không để xảy ra lỗi ngoại lệ chưa bắt (Unhandled ZeroDivisionError) làm sập hệ thống hoặc trả mã lỗi HTTP 500 cho người dùng.
+- Tuyệt đối không tự ý cộng thêm một số epsilon ngẫu nhiên vào điểm số nếu điều đó làm xáo trộn thứ tự tự nhiên của các bản ghi.
+- Tuyệt đối không loại bỏ toàn bộ kết quả tìm kiếm chỉ vì một trong hai kênh gặp hiện tượng điểm số phẳng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng phương sai bằng không (Zero Variance / Score Degeneracy) xảy ra khi tất cả các tài liệu đều có khoảng cách vector giống hệt nhau tới query. Một hàm chuẩn hóa điểm số bền bỉ (Robust Normalizer) bắt buộc phải có điều kiện rẽ nhánh: `if max_score == min_score: return [0.0] * len(scores)`, bảo đảm hệ thống hoạt động ổn định và tin cậy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Scikit-Learn Documentation: 'MinMaxScaler - Handling Zero Variance Features' &amp; Qdrant Score Normalization Guides</t>
         </is>
       </c>
     </row>
@@ -842,10 +878,33 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra định danh ổn định trước, rồi kiểm tra cách hợp các danh sách.
-Phân tích theo nguyên lý thiết kế: Kiểm tra định danh ổn định trước, rồi kiểm tra cách hợp các danh sách.</t>
+- [Chỉ rõ lỗi ghi đè điểm số RRF] (1.5 điểm): Phân tích công thức RRF yêu cầu cộng dồn 1/(k+rank) nhưng code lại ghi đè, làm mất điểm hạng 1 của A.
+- [Hậu quả đối với tài liệu A và B] (1.0 điểm): Chỉ ra việc A và B bị hạ điểm sai lệch và mất tính công bằng trong xếp hạng.
+- [Đặc tả cấu trúc trường đầu ra kiểm toán] (1.5 điểm): Thiết kế cấu trúc JSON lưu giữ final_rrf_score, mảng contributions từng nguồn và appearance_count.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra lỗi trong mã nguồn hiện tại (Defect Identification):
+- Thuật toán RRF (Reciprocal Rank Fusion) yêu cầu: Điểm số dung hợp của một tài liệu là **TỔNG CÁC ĐIỂM ĐÓNG GÓP TỶ LỆ NGHỊCH VỚI THỨ HẠNG** từ tất cả các danh sách tìm kiếm mà tài liệu đó xuất hiện: `RRF_Score(d) = sum_{m in Models} [ 1 / (k + rank_m(d)) ]`.
+- Đoạn code hiện tại bị lỗi **Ghi đè điểm số (Overwrite Defect)**: Khi tài liệu xuất hiện trong danh sách thứ hai, mã nguồn thay vì cộng dồn (`score += ...`) lại dùng phép gán đè (`score = ...`).
+- Hậu quả cụ thể:
+  + Tài liệu A (hạng 1 ở danh sách 1, hạng 3 ở danh sách 2): Bị ghi đè điểm số của hạng 3, mất hoàn toàn phần thưởng điểm cực lớn của hạng 1!
+  + Tài liệu B (hạng 2 ở cả hai danh sách): Bị mất một nửa điểm số vì hai lần đóng góp không được tích lũy. Cả hai tài liệu đều bị đánh giá sai lệch thứ tự nghiêm trọng.
+2. Các trường đầu ra cần lưu giữ để phục vụ kiểm tra và kiểm toán (Output Fields for Audit):
+Mỗi bản ghi đầu ra sau bước RRF phải chứa cấu trúc minh bạch sau:
+```json
+{
+  "doc_id": "A",
+  "final_rrf_score": 0.0325,
+  "contributions": [
+    {"source": "dense", "rank": 1, "score_added": 0.01639},
+    {"source": "sparse", "rank": 3, "score_added": 0.01587}
+  ],
+  "appearance_count": 2
+}
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bản chất của thuật toán RRF là cơ chế bỏ phiếu tích lũy (Cumulative Voting): một tài liệu xuất hiện ở thứ hạng cao trên nhiều danh sách độc lập phải được cộng gộp điểm để vươn lên vị trí dẫn đầu. Lỗi ghi đè điểm số làm biến RRF thành một phép lấy thứ tự của danh sách chạy sau, phá hủy hoàn toàn mục đích của Hybrid Search.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cormack, Clarke &amp; Büttcher (2009): 'Reciprocal Rank Fusion outperforms Condorcet and individual machine learning methods'</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1091,19 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra cây tài liệu và độ phủ của bản tóm tắt từng mục.
-Phân tích theo nguyên lý thiết kế: Kiểm tra cây tài liệu và độ phủ của bản tóm tắt từng mục.</t>
+- [Chẩn đoán đúng lỗi cắt tỉa nhánh sớm] (1.5 điểm): Chỉ ra bản tóm tắt mục cha thiếu ngoại lệ khiến thuật toán duyệt cây dừng sớm và bỏ lỡ phụ lục.
+- [Sửa bản tóm tắt mục cha] (1.5 điểm): Nêu giải pháp làm giàu tóm tắt cha bắt buộc chứa thông tin ngoại lệ và tham chiếu phụ lục.
+- [Thiết lập liên kết ngang có cấu trúc] (1.0 điểm): Bổ sung liên kết neo trực tiếp tới phụ lục mà không cần quét toàn bộ hệ thống tệp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán lỗi truy xuất cấu trúc (Defect Diagnosis):
+- Nguyên nhân: Quá trình duyệt cây cấu trúc (Tree Traversal / Structural Navigation) phụ thuộc vào tính toàn diện của bản tóm tắt mục cha (Section Summary). Bản tóm tắt mục cha đã bỏ qua (khuyết thiếu) thông tin về ngoại lệ nằm trong phụ lục. Khi thuật toán tìm kiếm duyệt từ gốc cây xuống, nó so khớp query với bản tóm tắt mục cha, thấy không liên quan nên quyết định **Cắt tỉa nhánh sớm (Early Tree Pruning)**, dẫn đến việc không bao giờ duyệt tới nút con phụ lục.
+2. Sửa chữa chỉ mục cấu trúc mà không dùng tìm kiếm quét phẳng toàn bộ tệp (Structural Index Repair):
+- Giải pháp 1 (Làm giàu bản tóm tắt mục cha - Summary Enrichment with Exceptions): Cập nhật quy trình sinh bản tóm tắt mục cha: bắt buộc trích xuất và đưa các từ khóa 'Ngoại lệ', 'Phụ lục', và các điều khoản miễn trừ đặc biệt vào phần tóm tắt của mục cha.
+- Giải pháp 2 (Bổ sung Liên kết ngang / Cross-linking &amp; Indexing of Leaves): Thiết lập các liên kết neo ngang (Anchor Cross-references) từ mục chính sách chính trỏ thẳng tới phụ lục, đồng thời duy trì một chỉ mục phụ (Leaf-level Inverted Index) cho toàn bộ các phần phụ lục ngoại lệ để hỗ trợ duyệt thẳng khi query chứa từ khóa ngoại lệ đặc thù.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong tìm kiếm cấu trúc phân cấp (Hierarchical Tree Retrieval / PageIndex), chất lượng điều hướng phụ thuộc hoàn toàn vào độ đại diện của các nút cha (Parent Node Summaries). Nếu nút cha làm rơi rụng thông tin của nút lá, cây sẽ bị cụt nhánh tìm kiếm. Việc làm giàu tóm tắt cha và duy trì liên kết trực tiếp là giải pháp căn cơ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Document Summary Index &amp; Tree-based Retrieval' (https://docs.llamaindex.ai)</t>
         </is>
       </c>
     </row>
@@ -1118,10 +1186,25 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định đường xử lý chính và điều kiện kích hoạt có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Xác định đường xử lý chính và điều kiện kích hoạt có thể quan sát.</t>
+- [Phân loại định tuyến theo loại tài liệu] (1.5 điểm): Phân định rõ tài liệu hướng dẫn dùng Structural Retriever, nhật ký hội thoại dùng Hybrid Dense+BM25.
+- [Thiết kế Fallback an toàn] (1.5 điểm): Thiết lập cơ chế fallback sang Hybrid Search khi Structural search thất bại.
+- [Tiết kiệm tài nguyên và độ trễ] (1.0 điểm): Nhấn mạnh quy tắc không gọi mọi retriever một cách mù quáng để bảo vệ SLO hệ thống.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Quy tắc Định tuyến Truy xuất (Retrieval Routing Rules):
+Không bao giờ gọi đồng thời mọi retriever cho mọi yêu cầu. Thiết lập bộ định tuyến thông minh (Smart Retriever Router) dựa trên thuộc tính tài liệu (Metadata Domain / Document Type) và đặc trưng truy vấn:
+- **Nhánh 1: Tài liệu có cấu trúc phân cấp (Hierarchical Structured Docs - Cẩm nang, Sổ tay chính sách)**:
+  + Kích hoạt: `Structural / PageIndex Retriever` (duyệt cây mục lục và các phần lồng nhau).
+  + Điều kiện dự phòng (Fallback Trigger): Nếu duyệt cấu trúc trả về điểm tin cậy thấp hoặc danh sách rỗng, kích hoạt fallback sang `Hybrid Dense+BM25 Retriever`.
+- **Nhánh 2: Nhật ký hội thoại &amp; Dữ liệu phẳng (Flat / Conversational Logs - Chat history, Ticket support)**:
+  + Kích hoạt trực tiếp: `Hybrid Dense+BM25 Retriever` (hoặc Time-window Filtered Search).
+  + Lý do: Nhật ký hội thoại không có cấu trúc cây, việc gọi Structural Retriever là hoàn toàn vô nghĩa và lãng phí độ trễ.
+2. Điều kiện kích hoạt có thể quan sát được (Observable Routing Invariants):
+- Kiểm tra metadata phân loại nguồn: `if doc_collection.type == 'hierarchical_manual': route_to(structural_pipeline)`.
+- Tối ưu hóa tài nguyên: Tiết kiệm 100% chi phí tính toán duyệt cây cho toàn bộ các truy vấn trên nhật ký hội thoại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một kiến trúc RAG doanh nghiệp trưởng thành phải có khả năng định tuyến đa đường (Multi-route Dispatching). Việc áp dụng một chiến lược truy xuất cấu trúc phân cấp cho một loại dữ liệu phi cấu trúc phẳng như chat log là sự lãng phí tài nguyên và làm tăng độ trễ không cần thiết.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Router Retrievers and Multi-Retrieval QA' &amp; LlamaIndex 'RouterQueryEngine'</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1283,24 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt bước chấm cặp query–tài liệu với candidate đầu vào.
-Phân tích theo nguyên lý thiết kế: Phân biệt bước chấm cặp query–tài liệu với candidate đầu vào.</t>
+- [Đánh giá bất khả thi của đề xuất] (1.5 điểm): Bác bỏ đề xuất chạy Cross-Encoder trên 2M chunk vì chi phí tính toán khổng lồ và vi phạm SLO độ trễ.
+- [Xác định đầu ra giai đoạn 1] (1.0 điểm): Nêu rõ giai đoạn 1 lọc 2 triệu chunk xuống Top 50-100 candidates bằng Bi-encoder/BM25.
+- [Vai trò thực sự của Cross-Encoder &amp; Trade-off metrics] (1.5 điểm): Xác định đúng vai trò reranker tinh chỉnh ở giai đoạn 2 và nêu các metric đo lường: Latency p95, NDCG@5, MRR.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá đề xuất chạy Cross-Encoder trên 2 triệu chunk:
+Đề xuất này là **HOÀN TOÀN BẤT KHẢ THI VÀ PHÁ VỠ HỆ THỐNG (Architecturally Unfeasible)**:
+- Phân tích độ phức tạp tính toán: Mô hình Cross-Encoder ghép cặp trực tiếp toàn bộ `(Query, Document)` và chạy qua toàn bộ các lớp Transformer Self-Attention. Nếu chạy trên 2 triệu chunk, chi phí tính toán là `2.000.000` lượt forward passes. Ngay cả trên cụm GPU cực mạnh, thời gian xử lý cho một truy vấn đơn lẻ sẽ mất từ vài phút đến hàng chục phút, vi phạm thảm khốc SLO độ trễ (thường quy định &lt; 200 ms).
+2. Đầu ra cần có của Giai đoạn đầu (First-Stage Retrieval Output):
+- Giai đoạn đầu sử dụng Bi-Encoder (Dense) kết hợp BM25 (Sparse) với chỉ mục HNSW/Inverted Index để lọc nhanh từ 2 triệu chunk xuống tập ứng viên nhỏ gọn (Candidate Set): chính xác **Top-50 đến Top-100 chunks** (Candidate Depth).
+3. Vai trò thực sự của Cross-Encoder (Second-Stage Reranker):
+- Cross-Encoder chỉ đóng vai trò là **Bộ tái xếp hạng tinh chỉnh (Fine-grained Reranker)** ở giai đoạn hai, chỉ chấm điểm trên 50-100 ứng viên đã được chọn lọc từ giai đoạn một để đưa ra Top-5 chunk chất lượng nhất cho LLM.
+4. Các chỉ số đo lường Trade-off:
+- Độ trễ: Đo thời gian chạy p95 của Bi-Encoder vs Cross-Encoder trên Top-K ứng viên.
+- Hiệu năng: Đo NDCG@5 và MRR để định lượng mức tăng độ chính xác so với chi phí trễ tính bằng mili-giây.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc cốt lõi của Kiến trúc Truy xuất Hai Tầng (Two-Stage Retrieval Funnel): Giai đoạn 1 (Bi-Encoder) tối ưu hóa cho Tốc độ và Độ bao phủ (High Recall, Low Latency) trên hàng triệu tài liệu; Giai đoạn 2 (Cross-Encoder) tối ưu hóa cho Độ chính xác cao (High Precision, Deep Cross-Attention) trên vài chục ứng viên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nogueira &amp; Cho (2019): 'Passage Re-ranking with BERT' &amp; Cohere Rerank Documentation</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1379,23 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra query relevance rồi đến redundancy với tập đã chọn.
-Phân tích theo nguyên lý thiết kế: Kiểm tra query relevance rồi đến redundancy với tập đã chọn.</t>
+- [Chẩn đoán chính xác lỗi của MMR] (1.5 điểm): Giải thích công thức MMR và chỉ ra việc giảm lambda quá thấp khiến phần phạt trùng lặp lấn át độ liên quan, chọn chunk lạc đề.
+- [Điều chỉnh tham số &amp; Ngưỡng sàn] (1.5 điểm): Đưa lambda về khoảng 0.5-0.7 và thiết lập Relevance Floor Threshold sàng lọc ứng viên.
+- [Thiết kế bước hậu kiểm] (1.0 điểm): Định nghĩa bước assertion kiểm tra mọi chunk được chọn đều thỏa mãn ngưỡng liên quan tối thiểu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán nguyên nhân lỗi (Root Cause Diagnosis):
+- Thuật toán MMR (Maximal Marginal Relevance) cân bằng giữa hai yếu tố: Độ liên quan với truy vấn (`Sim(Query, Doc)`) và Độ đa dạng / Độ mới so với các tài liệu đã chọn (`- Sim(Doc, Selected_Docs)`):
+  `MMR = argmax [ lambda * Sim(Query, d) - (1 - lambda) * max_{d_j in S} Sim(d, d_j) ]`.
+- Khi người vận hành tăng trọng số Diversity quá mức (tức là giảm `lambda` quá thấp, ví dụ `lambda = 0.1`), phần phạt trùng lặp lấn át hoàn toàn điểm liên quan. Hệ thống ưu tiên chọn một chunk chỉ vì nó 'càng khác các chunk đã chọn càng tốt', bất chấp việc chunk đó hoàn toàn lạc đề so với câu hỏi của người dùng.
+2. Điều chỉnh quy tắc lựa chọn (Selection Rule Adjustment):
+- Khôi phục trọng số cân bằng: Điều chỉnh tham số `lambda` về vùng an toàn tối ưu thực nghiệm, thường là `lambda in [0.5, 0.7]` (ưu tiên độ liên quan chiếm 50% - 70% quyết định).
+- Thiết lập Ngưỡng liên quan tối thiểu trước khi đa dạng hóa (Relevance Floor / Gating Threshold): Chỉ đưa các tài liệu có `Sim(Query, d) &gt;= min_relevance_threshold` (ví dụ &gt;= 0.70) vào tập ứng viên chạy MMR. Các tài liệu dưới ngưỡng này bị loại bỏ ngay từ đầu, không bao giờ được chọn dù có khác biệt đến đâu.
+3. Bước hậu kiểm bảo đảm không chọn chunk lạc đề (Post-selection Verification):
+- Chạy bộ kiểm tra tự động: `assert all(Sim(Query, doc) &gt;= min_relevance_threshold for doc in selected_chunks)` trước khi đóng gói context chuyển sang LLM.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Đa dạng hóa thông tin (Diversity) chỉ có ý nghĩa khi nằm trong ranh giới của sự liên quan (Relevance). Nếu không có ngưỡng sàn về độ liên quan (Relevance Floor), việc tối đa hóa độ đa dạng sẽ nhanh chóng biến thành việc thu thập các đoạn văn bản rác và lạc đề vào ngữ cảnh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Carbonell &amp; Goldstein (1998): 'The Use of MMR, Diversity-Based Reranking for Reordering Documents and Producing Summaries' (SIGIR '98)</t>
         </is>
       </c>
     </row>
@@ -1364,10 +1474,24 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt độ sâu candidate với độ sâu cuối; lỗi ở đây nằm trước reranking.
-Phân tích theo nguyên lý thiết kế: Phân biệt độ sâu candidate với độ sâu cuối; lỗi ở đây nằm trước reranking.</t>
+- [Chỉ rõ giới hạn của Cross-Encoder] (1.5 điểm): Khẳng định Cross-Encoder không thể phục hồi tài liệu vắng mặt trong Top-50 của giai đoạn 1.
+- [Đề xuất thí nghiệm ở tầng First-stage] (1.5 điểm): Đưa ra các giải pháp đúng tầng: tăng candidate depth (Top-100/200), Hybrid search, Query expansion.
+- [Thành phần giữ cố định] (1.0 điểm): Nêu rõ việc giữ cố định Cross-Encoder và tập benchmark để đo lường đối chứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định giới hạn kỹ thuật (Retriever Funnel Upper Bound):
+- Giới hạn căn bản: **Mô hình Cross-Encoder ở giai đoạn hai KHÔNG THỂ xếp hạng một tài liệu mà nó KHÔNG NHẬN ĐƯỢC từ giai đoạn một!** (Garbage In, Nothing Out Principle).
+- Recall@50 của giai đoạn đầu là trần tối đa (Upper Bound) cho toàn bộ pipeline. Nếu bằng chứng cần thiết không lọt vào Top-50 của Bi-Encoder/BM25, thì dù Cross-Encoder có thông minh và chính xác đến đâu, nó cũng hoàn toàn bất lực trong việc phục hồi bằng chứng đó. Tập trung tối ưu Cross-Encoder lúc này là đi sai tầng giải pháp.
+2. Đề xuất thí nghiệm ở đúng tầng kiến trúc (First-Stage Retrieval Experiments):
+- Thí nghiệm 1: Mở rộng độ sâu ứng viên (Candidate Pool Expansion) từ Top-50 lên Top-100 hoặc Top-200 để kiểm tra xem bằng chứng có nằm ở các thứ hạng tiếp theo hay không.
+- Thí nghiệm 2: Cải tiến tầng tìm kiếm giai đoạn đầu: Chuyển từ tìm kiếm đơn thuần sang Hybrid Search (kết hợp Dense + BM25 với RRF) hoặc áp dụng Query Expansion / HyDE để cải thiện khả năng thu hồi bằng chứng.
+- Thí nghiệm 3: Kiểm tra lại kích thước chunk và overlap ở tầng Ingestion.
+3. Thành phần cần giữ cố định khi kiểm tra (Controlled Baseline):
+- Giữ cố định 100% mô hình và trọng số của Cross-Encoder Reranker.
+- Giữ cố định tập dữ liệu kiểm thử (Evaluation Dataset) và câu hỏi truy vấn chuẩn để đo lường chính xác mức tăng Recall@Candidate của giai đoạn một.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong phễu truy xuất hai tầng (Retrieve-and-Rerank Funnel), giai đoạn 1 phụ trách Recall (độ bao phủ), giai đoạn 2 phụ trách Precision (độ chuẩn xác). Khi gặp lỗi thiếu bằng chứng (Recall Defect), mọi nỗ lực phải dồn vào việc cải tiến giai đoạn 1, vì giai đoạn 2 chỉ làm nhiệm vụ sắp xếp lại những gì đã được tìm thấy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cohere Rerank Documentation: 'Understanding Retrieval Funnels &amp; Candidate Depths' &amp; BEIR Benchmark Guidelines</t>
         </is>
       </c>
     </row>
